--- a/artfynd/A 496-2024 artfynd.xlsx
+++ b/artfynd/A 496-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>114876977</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114876979</v>
+        <v>114876978</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641712</v>
+        <v>641685</v>
       </c>
       <c r="R3" t="n">
-        <v>7174275</v>
+        <v>7174269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114876980</v>
+        <v>114876979</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641793</v>
+        <v>641712</v>
       </c>
       <c r="R4" t="n">
-        <v>7174263</v>
+        <v>7174275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114876985</v>
+        <v>114876980</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,7 +1017,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1046,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641926</v>
+        <v>641793</v>
       </c>
       <c r="R5" t="n">
-        <v>7174379</v>
+        <v>7174263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,6 +1085,312 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114876981</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>641843</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7174221</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114876982</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>641972</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7174333</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114876985</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>641926</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7174379</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 496-2024 artfynd.xlsx
+++ b/artfynd/A 496-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114876977</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114876978</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114876979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114876980</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114876981</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114876982</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,8 +1426,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114876985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>